--- a/Documentos Version 3.0/Product_Backlog_ICARO_V3.xlsx
+++ b/Documentos Version 3.0/Product_Backlog_ICARO_V3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Version 3.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA519AC6-1A34-4912-8319-59FD0038BD39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F7D838-4783-473D-A49F-3DB9C16B59DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Matriz CU-HU" sheetId="3" r:id="rId3"/>
     <sheet name="Historias Técnicas" sheetId="4" r:id="rId4"/>
     <sheet name="Product Backlog" sheetId="5" r:id="rId5"/>
-    <sheet name="Hoja1" sheetId="6" r:id="rId6"/>
+    <sheet name="Product Backlog " sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5309,7 +5309,7 @@
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="45">
+    <row r="1" spans="1:9" ht="15">
       <c r="A1" s="6" t="s">
         <v>433</v>
       </c>
